--- a/stories/arbres/TREE-AUT-038.xlsx
+++ b/stories/arbres/TREE-AUT-038.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Lila est avec maman, dans le salon. Lila a envie de jouer. maman est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila écoute maman. Lila entend les mots : reprendre ses affaires, avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2039,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Lila respire. Lila retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2230,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2397,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2537,6 +2590,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2701,6 +2759,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2863,6 +2926,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3025,6 +3093,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3187,6 +3260,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3349,6 +3427,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3511,6 +3594,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3673,6 +3761,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3861,6 +3954,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4025,6 +4123,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4187,6 +4290,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4349,6 +4457,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4511,6 +4624,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4673,6 +4791,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4835,6 +4958,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4997,6 +5125,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5185,6 +5318,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5349,6 +5487,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5511,6 +5654,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5673,6 +5821,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5835,6 +5988,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5997,6 +6155,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6159,6 +6322,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6183,7 +6351,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6321,6 +6489,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6501,6 +6675,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -6669,6 +6848,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Lila respire. Lila retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6855,6 +7039,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7017,6 +7206,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7205,6 +7399,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7369,6 +7568,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7531,6 +7735,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7693,6 +7902,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7855,6 +8069,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8017,6 +8236,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8179,6 +8403,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8341,6 +8570,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8529,6 +8763,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8693,6 +8932,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8855,6 +9099,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9017,6 +9266,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. La couverture est douce. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9179,6 +9433,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9341,6 +9600,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9503,6 +9767,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9665,6 +9934,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9853,6 +10127,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10017,6 +10296,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10179,6 +10463,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10341,6 +10630,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10503,6 +10797,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10665,6 +10964,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10827,6 +11131,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10851,7 +11160,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10989,6 +11298,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11169,6 +11484,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -11337,6 +11657,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Lila respire. Lila retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11523,6 +11848,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11685,6 +12015,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11873,6 +12208,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12037,6 +12377,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12199,6 +12544,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12361,6 +12711,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12523,6 +12878,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12685,6 +13045,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. On entend un oiseau. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12847,6 +13212,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13009,6 +13379,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13197,6 +13572,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13361,6 +13741,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13523,6 +13908,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13685,6 +14075,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13847,6 +14242,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14009,6 +14409,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14171,6 +14576,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14333,6 +14743,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14521,6 +14936,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14685,6 +15105,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14847,6 +15272,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15009,6 +15439,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15171,6 +15606,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15333,6 +15773,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Le vent est doux. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15495,6 +15940,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15513,7 +15963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15586,6 +16036,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-038.xlsx
+++ b/stories/arbres/TREE-AUT-038.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Lila est avec maman, dans le salon. Lila a envie de jouer. maman est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila écoute maman. Lila entend les mots : reprendre ses affaires, avant de partir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2044,6 +2053,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Lila respire. Lila retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2235,6 +2245,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2402,6 +2413,7 @@
           <t>narrateur|Lila a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2597,6 +2609,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2764,6 +2777,7 @@
           <t>narrateur|Lila rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2931,6 +2945,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3098,6 +3113,7 @@
           <t>narrateur|Lila rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3265,6 +3281,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3432,6 +3449,7 @@
           <t>narrateur|Lila rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3599,6 +3617,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3766,6 +3785,7 @@
           <t>narrateur|Lila a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3961,6 +3981,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4128,6 +4149,7 @@
           <t>narrateur|Lila rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4295,6 +4317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4462,6 +4485,7 @@
           <t>narrateur|Lila rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4629,6 +4653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4796,6 +4821,7 @@
           <t>narrateur|Lila rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4963,6 +4989,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5130,6 +5157,7 @@
           <t>narrateur|Lila a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5325,6 +5353,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5492,6 +5521,7 @@
           <t>narrateur|Lila rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5659,6 +5689,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5826,6 +5857,7 @@
           <t>narrateur|Lila rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5993,6 +6025,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6160,6 +6193,7 @@
           <t>narrateur|Lila rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6327,6 +6361,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6495,6 +6530,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6682,6 +6718,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6853,6 +6890,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Lila respire. Lila retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7044,6 +7082,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7211,6 +7250,7 @@
           <t>narrateur|Lila a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7406,6 +7446,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7573,6 +7614,7 @@
           <t>narrateur|Lila rejoint Tom. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7740,6 +7782,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7907,6 +7950,7 @@
           <t>narrateur|Lila rejoint Léa. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8074,6 +8118,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8241,6 +8286,7 @@
           <t>narrateur|Lila rejoint Sami. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8408,6 +8454,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8575,6 +8622,7 @@
           <t>narrateur|Lila a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8770,6 +8818,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8937,6 +8986,7 @@
           <t>narrateur|Lila rejoint Tom. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9104,6 +9154,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9271,6 +9322,7 @@
           <t>narrateur|Lila rejoint Léa. La couverture est douce. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9438,6 +9490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9605,6 +9658,7 @@
           <t>narrateur|Lila rejoint Sami. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9772,6 +9826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9939,6 +9994,7 @@
           <t>narrateur|Lila a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10134,6 +10190,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10301,6 +10358,7 @@
           <t>narrateur|Lila rejoint Tom. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10468,6 +10526,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10635,6 +10694,7 @@
           <t>narrateur|Lila rejoint Léa. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10802,6 +10862,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10969,6 +11030,7 @@
           <t>narrateur|Lila rejoint Sami. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11136,6 +11198,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11304,6 +11367,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11491,6 +11555,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11662,6 +11727,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Lila respire. Lila retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11853,6 +11919,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12020,6 +12087,7 @@
           <t>narrateur|Lila a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12215,6 +12283,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12382,6 +12451,7 @@
           <t>narrateur|Lila rejoint Tom. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12549,6 +12619,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12716,6 +12787,7 @@
           <t>narrateur|Lila rejoint Léa. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12883,6 +12955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13050,6 +13123,7 @@
           <t>narrateur|Lila rejoint Sami. On entend un oiseau. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13217,6 +13291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13384,6 +13459,7 @@
           <t>narrateur|Lila a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13579,6 +13655,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13746,6 +13823,7 @@
           <t>narrateur|Lila rejoint Tom. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13913,6 +13991,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14080,6 +14159,7 @@
           <t>narrateur|Lila rejoint Léa. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14247,6 +14327,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14414,6 +14495,7 @@
           <t>narrateur|Lila rejoint Sami. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14581,6 +14663,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14748,6 +14831,7 @@
           <t>narrateur|Lila a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14943,6 +15027,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15110,6 +15195,7 @@
           <t>narrateur|Lila rejoint Tom. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15277,6 +15363,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15444,6 +15531,7 @@
           <t>narrateur|Lila rejoint Léa. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15611,6 +15699,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15778,6 +15867,7 @@
           <t>narrateur|Lila rejoint Sami. Le vent est doux. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15945,6 +16035,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15963,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16043,6 +16134,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16244,6 +16349,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-038.xlsx
+++ b/stories/arbres/TREE-AUT-038.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Retrouver ses affaires avant de partir — dans le salon</t>
+          <t>Le seau sous la table</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un carré de soleil dort sur le tapis. Mila joue au parc, puis elle cherche seau et manteau avant de partir.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Lila est avec maman, dans le salon. Lila a envie de jouer. maman est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila écoute maman. Lila entend les mots : reprendre ses affaires, avant de partir.</t>
+          <t>Un carré de soleil dort sur le tapis. Le tapis est rouge, tout doux. Une mouche marche sur le pain. Le pain est encore tiède. Ça sent bon, tout près. Un manteau rouge est sur le fauteuil. Le fauteuil est un peu creux. Un seau jaune est sous la table. Le seau a du sable au fond. Un doudou montre une oreille. Il est dans le canapé. Maman secoue une serviette. Des miettes tombent, toutes petites. Papa noue un lacet. Le lacet fait un petit bruit. Tu as vu le soleil, Mila ? Oui, maman. Il est chaud. En ce moment, Mila touche le seau. Le seau est un peu rêche. Je veux le parc ! On y va. Puis on reprend tes affaires. Mila va reprendre ses affaires. Avant de partir. On cherche seau et manteau. On les prend. Oui, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,7 +1337,34 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Lila est avec maman, dans le salon. Lila a envie de jouer. maman est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila écoute maman. Lila entend les mots : reprendre ses affaires, avant de partir.</t>
+          <t>narrateur|Un carré de soleil dort sur le tapis.
+narrateur|Le tapis est rouge, tout doux.
+narrateur|Une mouche marche sur le pain.
+narrateur|Le pain est encore tiède.
+narrateur|Ça sent bon, tout près.
+narrateur|Un manteau rouge est sur le fauteuil.
+narrateur|Le fauteuil est un peu creux.
+narrateur|Un seau jaune est sous la table.
+narrateur|Le seau a du sable au fond.
+narrateur|Un doudou montre une oreille.
+narrateur|Il est dans le canapé.
+narrateur|Maman secoue une serviette.
+narrateur|Des miettes tombent, toutes petites.
+narrateur|Papa noue un lacet.
+narrateur|Le lacet fait un petit bruit.
+maman|Tu as vu le soleil, Mila ?
+enfant-f|Oui, maman.
+enfant-f|Il est chaud.
+narrateur|En ce moment, Mila touche le seau.
+narrateur|Le seau est un peu rêche.
+enfant-f|Je veux le parc !
+maman|On y va.
+papa|Puis on reprend tes affaires.
+narrateur|Mila va reprendre ses affaires.
+maman|Avant de partir.
+papa|On cherche seau et manteau.
+papa|On les prend.
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1353,7 +1392,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>Le parc a trois coins. Le bac à sable. Le toboggan. Ou les balançoires ? On joue. Après, tes affaires.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1521,7 +1560,12 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|Le parc a trois coins.
+papa|Le bac à sable.
+papa|Le toboggan.
+maman|Ou les balançoires ?
+maman|On joue.
+maman|Après, tes affaires.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1549,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On range un objet. Je suis là. On reste ensemble.</t>
+          <t>Mila s'agenouille au bac. Le sable est frais. Ça fait chh, sous la main. Le seau jaune sonne. Un château, maman. D'accord. Le seau reste près de toi. Le manteau est sur le banc. Mila verse le sable. Ça sent la terre propre. Avant de partir, on cherche. On reprend tes affaires. Le seau et le manteau. Oui. On les prend. Un grain reste sous l'ongle. Bravo. Tes affaires t'attendent.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1689,8 +1733,22 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Lila va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On range un objet.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Mila s'agenouille au bac.
+narrateur|Le sable est frais.
+narrateur|Ça fait chh, sous la main.
+narrateur|Le seau jaune sonne.
+enfant-f|Un château, maman.
+maman|D'accord.
+papa|Le seau reste près de toi.
+maman|Le manteau est sur le banc.
+narrateur|Mila verse le sable.
+narrateur|Ça sent la terre propre.
+papa|Avant de partir, on cherche.
+maman|On reprend tes affaires.
+enfant-f|Le seau et le manteau.
+papa|Oui. On les prend.
+narrateur|Un grain reste sous l'ongle.
+maman|Bravo. Tes affaires t'attendent.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1718,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>Mila joue au bac. Avant de partir, on fait quoi ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1878,7 +1936,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>narrateur|Mila joue au bac.
+maman|Avant de partir, on fait quoi ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1906,7 +1965,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Lila respire. Lila retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>Oui. Reprendre ses affaires. Avant de partir. On cherche le seau. On cherche le manteau. On les prend. Le seau, puis le manteau. Bravo, Mila. C'est du bon travail. Un grain reste au bord.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2050,7 +2109,16 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Lila respire. Lila retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>maman|Oui.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|On cherche le seau.
+narrateur|On cherche le manteau.
+narrateur|On les prend.
+enfant-f|Le seau, puis le manteau.
+maman|Bravo, Mila.
+papa|C'est du bon travail.
+narrateur|Un grain reste au bord.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2078,7 +2146,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Mila peut encore jouer, près du bac. Le ballon, le seau, ou le doudou ? Tu choisis. Après, on reprend tes affaires.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2242,7 +2310,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Mila peut encore jouer, près du bac.
+maman|Le ballon, le seau, ou le doudou ?
+papa|Tu choisis.
+papa|Après, on reprend tes affaires.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2270,7 +2341,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Près du bac, le ballon attend. Il est un peu mou. Le ballon rouge. Oui. Tout doux. Le seau reste à droite. Quand c'est l'heure, on cherche. On reprend tes affaires. Avant de partir. Je cherche. Puis on les prend. Mila pose encore une main. Le sable fait chh. Tu as fini ce jeu ? Presque. D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2410,7 +2481,21 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>narrateur|Près du bac, le ballon attend.
+narrateur|Il est un peu mou.
+enfant-f|Le ballon rouge.
+papa|Oui. Tout doux.
+maman|Le seau reste à droite.
+papa|Quand c'est l'heure, on cherche.
+maman|On reprend tes affaires.
+maman|Avant de partir.
+enfant-f|Je cherche.
+papa|Puis on les prend.
+narrateur|Mila pose encore une main.
+narrateur|Le sable fait chh.
+maman|Tu as fini ce jeu ?
+enfant-f|Presque.
+papa|D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2438,7 +2523,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire. Le manteau, le seau, ou le doudou ? On cherche. On prend. Reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2606,7 +2691,11 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire.
+maman|Le manteau, le seau, ou le doudou ?
+papa|On cherche. On prend.
+maman|Reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2634,7 +2723,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le bac à sable. Le ballon a un grain de sable. Mila cherche d'abord le manteau. Le manteau rouge est au banc. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend aussi le seau. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le carré de soleil a glissé.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2774,7 +2863,25 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le bac à sable.
+narrateur|Le ballon a un grain de sable.
+narrateur|Mila cherche d'abord le manteau.
+narrateur|Le manteau rouge est au banc.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend aussi le seau.
+papa|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le carré de soleil a glissé.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2802,7 +2909,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Un grain reste au bord du bac. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2942,7 +3049,14 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Un grain reste au bord du bac.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2970,7 +3084,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le bac à sable. Le ballon est un peu mou, encore. Mila cherche d'abord le seau. Le seau jaune sonne. On cherche. On prend. Je le prends. Bravo. Maintenant le manteau. Mila prend le manteau au banc. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le tapis rouge est un peu vide.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3110,7 +3224,25 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le bac à sable.
+narrateur|Le ballon est un peu mou, encore.
+narrateur|Mila cherche d'abord le seau.
+narrateur|Le seau jaune sonne.
+maman|On cherche. On prend.
+enfant-f|Je le prends.
+papa|Bravo. Maintenant le manteau.
+narrateur|Mila prend le manteau au banc.
+maman|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le tapis rouge est un peu vide.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3138,7 +3270,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Un grain reste au bord du bac. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3278,7 +3410,14 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Un grain reste au bord du bac.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3306,7 +3445,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le bac à sable. Le ballon sent le soleil. Mila cherche d'abord le doudou. Le doudou a une oreille dehors. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend le seau, puis le manteau. Tes affaires. J'ai tout. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Une miette dort encore au salon.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3446,7 +3585,25 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le bac à sable.
+narrateur|Le ballon sent le soleil.
+narrateur|Mila cherche d'abord le doudou.
+narrateur|Le doudou a une oreille dehors.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend le seau, puis le manteau.
+papa|Tes affaires.
+enfant-f|J'ai tout.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Une miette dort encore au salon.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3474,7 +3631,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Un grain reste au bord du bac. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3614,7 +3771,14 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Un grain reste au bord du bac.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3642,7 +3806,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+          <t>Près du bac, le seau sonne. Il est jaune, un peu rêche. Je verse. Oui. Tout doux. Le manteau reste au banc. Quand c'est l'heure, on cherche. On reprend tes affaires. Avant de partir. Je cherche. Puis on les prend. Mila pose encore une main. Le sable fait chh. Tu as fini ce jeu ? Presque. D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3782,7 +3946,21 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+          <t>narrateur|Près du bac, le seau sonne.
+narrateur|Il est jaune, un peu rêche.
+enfant-f|Je verse.
+maman|Oui. Tout doux.
+papa|Le manteau reste au banc.
+papa|Quand c'est l'heure, on cherche.
+maman|On reprend tes affaires.
+maman|Avant de partir.
+enfant-f|Je cherche.
+papa|Puis on les prend.
+narrateur|Mila pose encore une main.
+narrateur|Le sable fait chh.
+maman|Tu as fini ce jeu ?
+enfant-f|Presque.
+papa|D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3810,7 +3988,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire. Le manteau, le seau, ou le doudou ? On cherche. On prend. Reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3978,7 +4156,11 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire.
+maman|Le manteau, le seau, ou le doudou ?
+papa|On cherche. On prend.
+maman|Reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4006,7 +4188,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le bac à sable. Le seau a du sable au fond. Mila cherche d'abord le manteau. Le manteau rouge est au banc. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend aussi le seau. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le pain n'est plus tiède.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4146,7 +4328,25 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le bac à sable.
+narrateur|Le seau a du sable au fond.
+narrateur|Mila cherche d'abord le manteau.
+narrateur|Le manteau rouge est au banc.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend aussi le seau.
+papa|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le pain n'est plus tiède.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4174,7 +4374,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Un grain reste au bord du bac. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4314,7 +4514,14 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Un grain reste au bord du bac.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4342,7 +4549,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le bac à sable. Le seau sonne contre le bois. Mila cherche d'abord le seau. Le seau jaune sonne. On cherche. On prend. Je le prends. Bravo. Maintenant le manteau. Mila prend le manteau au banc. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. La mouche a quitté le pain.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4482,7 +4689,25 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le bac à sable.
+narrateur|Le seau sonne contre le bois.
+narrateur|Mila cherche d'abord le seau.
+narrateur|Le seau jaune sonne.
+maman|On cherche. On prend.
+enfant-f|Je le prends.
+papa|Bravo. Maintenant le manteau.
+narrateur|Mila prend le manteau au banc.
+maman|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|La mouche a quitté le pain.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4510,7 +4735,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Un grain reste au bord du bac. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4650,7 +4875,14 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Un grain reste au bord du bac.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4678,7 +4910,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le bac à sable. Le seau est rêche, sous les doigts. Mila cherche d'abord le doudou. Le doudou a une oreille dehors. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend le seau, puis le manteau. Tes affaires. J'ai tout. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le fauteuil reste un peu creux.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4818,7 +5050,25 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le bac à sable.
+narrateur|Le seau est rêche, sous les doigts.
+narrateur|Mila cherche d'abord le doudou.
+narrateur|Le doudou a une oreille dehors.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend le seau, puis le manteau.
+papa|Tes affaires.
+enfant-f|J'ai tout.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le fauteuil reste un peu creux.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4846,7 +5096,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Un grain reste au bord du bac. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4986,7 +5236,14 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Un grain reste au bord du bac.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5014,7 +5271,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Près du bac, le doudou veille. Une oreille dépasse. Il a du sable. On le secoue, tout doux. Le seau reste près de toi. Quand c'est l'heure, on cherche. On reprend tes affaires. Avant de partir. Je cherche. Puis on les prend. Mila pose encore une main. Le sable fait chh. Tu as fini ce jeu ? Presque. D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5154,7 +5411,21 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>narrateur|Près du bac, le doudou veille.
+narrateur|Une oreille dépasse.
+enfant-f|Il a du sable.
+maman|On le secoue, tout doux.
+papa|Le seau reste près de toi.
+papa|Quand c'est l'heure, on cherche.
+maman|On reprend tes affaires.
+maman|Avant de partir.
+enfant-f|Je cherche.
+papa|Puis on les prend.
+narrateur|Mila pose encore une main.
+narrateur|Le sable fait chh.
+maman|Tu as fini ce jeu ?
+enfant-f|Presque.
+papa|D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5182,7 +5453,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire. Le manteau, le seau, ou le doudou ? On cherche. On prend. Reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5350,7 +5621,11 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire.
+maman|Le manteau, le seau, ou le doudou ?
+papa|On cherche. On prend.
+maman|Reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5378,7 +5653,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le bac à sable. Le doudou a un grain sur l'oreille. Mila cherche d'abord le manteau. Le manteau rouge est au banc. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend aussi le seau. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le canapé n'a plus d'oreille.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5518,7 +5793,25 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le bac à sable.
+narrateur|Le doudou a un grain sur l'oreille.
+narrateur|Mila cherche d'abord le manteau.
+narrateur|Le manteau rouge est au banc.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend aussi le seau.
+papa|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le canapé n'a plus d'oreille.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5546,7 +5839,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Un grain reste au bord du bac. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5686,7 +5979,14 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Un grain reste au bord du bac.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5714,7 +6014,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le bac à sable. Le doudou sent le vent du bac. Mila cherche d'abord le seau. Le seau jaune sonne. On cherche. On prend. Je le prends. Bravo. Maintenant le manteau. Mila prend le manteau au banc. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le lacet de papa est noué.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5854,7 +6154,25 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le bac à sable.
+narrateur|Le doudou sent le vent du bac.
+narrateur|Mila cherche d'abord le seau.
+narrateur|Le seau jaune sonne.
+maman|On cherche. On prend.
+enfant-f|Je le prends.
+papa|Bravo. Maintenant le manteau.
+narrateur|Mila prend le manteau au banc.
+maman|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le lacet de papa est noué.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5882,7 +6200,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Un grain reste au bord du bac. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6022,7 +6340,14 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Un grain reste au bord du bac.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6050,7 +6375,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le bac à sable. Le doudou est chaud, contre Mila. Mila cherche d'abord le doudou. Le doudou a une oreille dehors. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend le seau, puis le manteau. Tes affaires. J'ai tout. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. La serviette de maman est pliée.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6190,7 +6515,25 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le bac à sable.
+narrateur|Le doudou est chaud, contre Mila.
+narrateur|Mila cherche d'abord le doudou.
+narrateur|Le doudou a une oreille dehors.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend le seau, puis le manteau.
+papa|Tes affaires.
+enfant-f|J'ai tout.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|La serviette de maman est pliée.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6218,7 +6561,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Un grain reste au bord du bac. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6358,7 +6701,14 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Un grain reste au bord du bac.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6386,7 +6736,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Mila va vers le toboggan. Le métal est un peu tiède. Une marche est lisse. Je glisse, papa ? Oui. Tout doux. Le manteau reste au banc. Le seau reste en bas. Mila glisse une fois. Ça fait un petit vent. Avant de partir, on cherche. On reprend tes affaires. Je cherche. On les prend, après. Le toboggan redevient calme. Bravo, Mila. Une feuille passe tout haut.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6526,8 +6876,22 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Lila va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On dit merci.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Mila va vers le toboggan.
+narrateur|Le métal est un peu tiède.
+narrateur|Une marche est lisse.
+enfant-f|Je glisse, papa ?
+papa|Oui. Tout doux.
+maman|Le manteau reste au banc.
+papa|Le seau reste en bas.
+narrateur|Mila glisse une fois.
+narrateur|Ça fait un petit vent.
+maman|Avant de partir, on cherche.
+maman|On reprend tes affaires.
+enfant-f|Je cherche.
+papa|On les prend, après.
+narrateur|Le toboggan redevient calme.
+maman|Bravo, Mila.
+narrateur|Une feuille passe tout haut.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6555,7 +6919,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>Mila a glissé. Avant de partir, on fait quoi ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6715,7 +7079,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>narrateur|Mila a glissé.
+papa|Avant de partir, on fait quoi ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6743,7 +7108,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Lila respire. Lila retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>Oui. Reprendre ses affaires. Avant de partir. On cherche le seau. On cherche le manteau. On les prend. Je cherche. Bravo. C'est du bon travail. Le métal est encore tiède.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6887,7 +7252,16 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Lila respire. Lila retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>papa|Oui.
+papa|Reprendre ses affaires.
+maman|Avant de partir.
+narrateur|On cherche le seau.
+narrateur|On cherche le manteau.
+narrateur|On les prend.
+enfant-f|Je cherche.
+maman|Bravo.
+papa|C'est du bon travail.
+narrateur|Le métal est encore tiède.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6915,7 +7289,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Mila peut encore jouer, près du toboggan. Le ballon, le seau, ou le doudou ? Tu choisis. Après, on reprend tes affaires.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7079,7 +7453,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Mila peut encore jouer, près du toboggan.
+maman|Le ballon, le seau, ou le doudou ?
+papa|Tu choisis.
+papa|Après, on reprend tes affaires.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7107,7 +7484,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Près du toboggan, le ballon attend. Il a roulé au pied. Je le pousse. Tout doux, Mila. Le manteau reste au banc. Quand c'est l'heure, on cherche. On reprend tes affaires. Avant de partir. Je cherche. Puis on les prend. Mila touche encore le métal. Il est tiède. Tu as fini ce jeu ? Oui, bientôt. D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7247,7 +7624,21 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>narrateur|Près du toboggan, le ballon attend.
+narrateur|Il a roulé au pied.
+enfant-f|Je le pousse.
+papa|Tout doux, Mila.
+maman|Le manteau reste au banc.
+maman|Quand c'est l'heure, on cherche.
+papa|On reprend tes affaires.
+papa|Avant de partir.
+enfant-f|Je cherche.
+maman|Puis on les prend.
+narrateur|Mila touche encore le métal.
+narrateur|Il est tiède.
+papa|Tu as fini ce jeu ?
+enfant-f|Oui, bientôt.
+maman|D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7275,7 +7666,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire. Le manteau, le seau, ou le doudou ? On cherche. On prend. Reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7443,7 +7834,11 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire.
+maman|Le manteau, le seau, ou le doudou ?
+papa|On cherche. On prend.
+maman|Reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7471,7 +7866,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le toboggan. Le ballon attend au pied du toboggan. Mila cherche d'abord le manteau. Le manteau rouge est au banc. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend aussi le seau. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le salon sent encore le pain.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7611,7 +8006,25 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le toboggan.
+narrateur|Le ballon attend au pied du toboggan.
+narrateur|Mila cherche d'abord le manteau.
+narrateur|Le manteau rouge est au banc.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend aussi le seau.
+papa|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le salon sent encore le pain.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7639,7 +8052,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Le métal du toboggan refroidit. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7779,7 +8192,14 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Le métal du toboggan refroidit.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7807,7 +8227,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le toboggan. Le ballon a roulé tout près. Mila cherche d'abord le seau. Le seau jaune sonne. On cherche. On prend. Je le prends. Bravo. Maintenant le manteau. Mila prend le manteau au banc. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le tapis a perdu son carré.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7947,7 +8367,25 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le toboggan.
+narrateur|Le ballon a roulé tout près.
+narrateur|Mila cherche d'abord le seau.
+narrateur|Le seau jaune sonne.
+maman|On cherche. On prend.
+enfant-f|Je le prends.
+papa|Bravo. Maintenant le manteau.
+narrateur|Mila prend le manteau au banc.
+maman|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le tapis a perdu son carré.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7975,7 +8413,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Le métal du toboggan refroidit. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8115,7 +8553,14 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Le métal du toboggan refroidit.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8143,7 +8588,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le toboggan. Le ballon est tiède, comme le métal. Mila cherche d'abord le doudou. Le doudou a une oreille dehors. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend le seau, puis le manteau. Tes affaires. J'ai tout. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Une ombre a pris la place.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8283,7 +8728,25 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le toboggan.
+narrateur|Le ballon est tiède, comme le métal.
+narrateur|Mila cherche d'abord le doudou.
+narrateur|Le doudou a une oreille dehors.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend le seau, puis le manteau.
+papa|Tes affaires.
+enfant-f|J'ai tout.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Une ombre a pris la place.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8311,7 +8774,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Le métal du toboggan refroidit. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8451,7 +8914,14 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Le métal du toboggan refroidit.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8479,7 +8949,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+          <t>Près du toboggan, le seau attend. Il est en bas, bien droit. Il me garde. Oui. Il t'attend. Le manteau aussi. Quand c'est l'heure, on cherche. On reprend tes affaires. Avant de partir. Je cherche. Puis on les prend. Mila touche encore le métal. Il est tiède. Tu as fini ce jeu ? Oui, bientôt. D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8619,7 +9089,21 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+          <t>narrateur|Près du toboggan, le seau attend.
+narrateur|Il est en bas, bien droit.
+enfant-f|Il me garde.
+maman|Oui. Il t'attend.
+papa|Le manteau aussi.
+maman|Quand c'est l'heure, on cherche.
+papa|On reprend tes affaires.
+papa|Avant de partir.
+enfant-f|Je cherche.
+maman|Puis on les prend.
+narrateur|Mila touche encore le métal.
+narrateur|Il est tiède.
+papa|Tu as fini ce jeu ?
+enfant-f|Oui, bientôt.
+maman|D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8647,7 +9131,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire. Le manteau, le seau, ou le doudou ? On cherche. On prend. Reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8815,7 +9299,11 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire.
+maman|Le manteau, le seau, ou le doudou ?
+papa|On cherche. On prend.
+maman|Reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8843,7 +9331,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le toboggan. Le seau garde le bas du toboggan. Mila cherche d'abord le manteau. Le manteau rouge est au banc. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend aussi le seau. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. La table n'a plus de seau.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8983,7 +9471,25 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le toboggan.
+narrateur|Le seau garde le bas du toboggan.
+narrateur|Mila cherche d'abord le manteau.
+narrateur|Le manteau rouge est au banc.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend aussi le seau.
+papa|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|La table n'a plus de seau.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9011,7 +9517,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Le métal du toboggan refroidit. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9151,7 +9657,14 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Le métal du toboggan refroidit.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9179,7 +9692,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. La couverture est douce. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le toboggan. Le seau a un peu de poussière. Mila cherche d'abord le seau. Le seau jaune sonne. On cherche. On prend. Je le prends. Bravo. Maintenant le manteau. Mila prend le manteau au banc. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le fauteuil n'a plus de manteau.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9319,7 +9832,25 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. La couverture est douce. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le toboggan.
+narrateur|Le seau a un peu de poussière.
+narrateur|Mila cherche d'abord le seau.
+narrateur|Le seau jaune sonne.
+maman|On cherche. On prend.
+enfant-f|Je le prends.
+papa|Bravo. Maintenant le manteau.
+narrateur|Mila prend le manteau au banc.
+maman|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le fauteuil n'a plus de manteau.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9347,7 +9878,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Le métal du toboggan refroidit. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9487,7 +10018,14 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Le métal du toboggan refroidit.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9515,7 +10053,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le toboggan. Le seau cliquette, tout bas. Mila cherche d'abord le doudou. Le doudou a une oreille dehors. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend le seau, puis le manteau. Tes affaires. J'ai tout. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le canapé est tout calme.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9655,7 +10193,25 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le toboggan.
+narrateur|Le seau cliquette, tout bas.
+narrateur|Mila cherche d'abord le doudou.
+narrateur|Le doudou a une oreille dehors.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend le seau, puis le manteau.
+papa|Tes affaires.
+enfant-f|J'ai tout.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le canapé est tout calme.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9683,7 +10239,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Le métal du toboggan refroidit. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9823,7 +10379,14 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Le métal du toboggan refroidit.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9851,7 +10414,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Près du toboggan, le doudou attend. Il est sur la marche basse. Il a vu. Oui. Il a vu. Le seau est en bas. Quand c'est l'heure, on cherche. On reprend tes affaires. Avant de partir. Je cherche. Puis on les prend. Mila touche encore le métal. Il est tiède. Tu as fini ce jeu ? Oui, bientôt. D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9991,7 +10554,21 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>narrateur|Près du toboggan, le doudou attend.
+narrateur|Il est sur la marche basse.
+enfant-f|Il a vu.
+papa|Oui. Il a vu.
+maman|Le seau est en bas.
+maman|Quand c'est l'heure, on cherche.
+papa|On reprend tes affaires.
+papa|Avant de partir.
+enfant-f|Je cherche.
+maman|Puis on les prend.
+narrateur|Mila touche encore le métal.
+narrateur|Il est tiède.
+papa|Tu as fini ce jeu ?
+enfant-f|Oui, bientôt.
+maman|D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10019,7 +10596,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire. Le manteau, le seau, ou le doudou ? On cherche. On prend. Reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10187,7 +10764,11 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire.
+maman|Le manteau, le seau, ou le doudou ?
+papa|On cherche. On prend.
+maman|Reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10215,7 +10796,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le toboggan. Le doudou a vu la descente. Mila cherche d'abord le manteau. Le manteau rouge est au banc. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend aussi le seau. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Une miette brille au salon.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10355,7 +10936,25 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le toboggan.
+narrateur|Le doudou a vu la descente.
+narrateur|Mila cherche d'abord le manteau.
+narrateur|Le manteau rouge est au banc.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend aussi le seau.
+papa|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Une miette brille au salon.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10383,7 +10982,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Le métal du toboggan refroidit. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10523,7 +11122,14 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Le métal du toboggan refroidit.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10551,7 +11157,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le toboggan. Le doudou est sur la marche basse. Mila cherche d'abord le seau. Le seau jaune sonne. On cherche. On prend. Je le prends. Bravo. Maintenant le manteau. Mila prend le manteau au banc. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le lacet ne fait plus de bruit.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10691,7 +11297,25 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le toboggan.
+narrateur|Le doudou est sur la marche basse.
+narrateur|Mila cherche d'abord le seau.
+narrateur|Le seau jaune sonne.
+maman|On cherche. On prend.
+enfant-f|Je le prends.
+papa|Bravo. Maintenant le manteau.
+narrateur|Mila prend le manteau au banc.
+maman|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le lacet ne fait plus de bruit.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10719,7 +11343,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Le métal du toboggan refroidit. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10859,7 +11483,14 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Le métal du toboggan refroidit.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10887,7 +11518,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte le toboggan. Le doudou a une odeur de métal chaud. Mila cherche d'abord le doudou. Le doudou a une oreille dehors. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend le seau, puis le manteau. Tes affaires. J'ai tout. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le pain attend sur la table.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11027,7 +11658,25 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte le toboggan.
+narrateur|Le doudou a une odeur de métal chaud.
+narrateur|Mila cherche d'abord le doudou.
+narrateur|Le doudou a une oreille dehors.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend le seau, puis le manteau.
+papa|Tes affaires.
+enfant-f|J'ai tout.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le pain attend sur la table.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11055,7 +11704,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. Le métal du toboggan refroidit. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11195,7 +11844,14 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Le métal du toboggan refroidit.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11223,7 +11879,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement. Je suis là. On reste ensemble.</t>
+          <t>Mila va vers les balançoires. Une chaîne fait tic, tic. Le siège est un peu lisse. Je balance, maman ? Oui. Tout doux. Le manteau est au banc. Le seau est à tes pieds. Mila va, vient, va, vient. Le vent touche sa joue. Avant de partir, on cherche. On reprend tes affaires. Le seau. Le manteau. Oui. On les prend. La chaîne se tait un peu. Bravo. Tes affaires t'attendent. Un oiseau passe au-dessus.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11363,8 +12019,22 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Lila va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Mila va vers les balançoires.
+narrateur|Une chaîne fait tic, tic.
+narrateur|Le siège est un peu lisse.
+enfant-f|Je balance, maman ?
+maman|Oui. Tout doux.
+papa|Le manteau est au banc.
+maman|Le seau est à tes pieds.
+narrateur|Mila va, vient, va, vient.
+narrateur|Le vent touche sa joue.
+papa|Avant de partir, on cherche.
+maman|On reprend tes affaires.
+enfant-f|Le seau. Le manteau.
+papa|Oui. On les prend.
+narrateur|La chaîne se tait un peu.
+maman|Bravo. Tes affaires t'attendent.
+narrateur|Un oiseau passe au-dessus.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11392,7 +12062,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>Mila s'est balancée. Avant de partir, on fait quoi ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11552,7 +12222,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>narrateur|Mila s'est balancée.
+maman|Avant de partir, on fait quoi ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11580,7 +12251,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Lila respire. Lila retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>Oui. Reprendre ses affaires. Avant de partir. On cherche le seau. On cherche le manteau. On les prend. J'ai compris. Bravo, Mila. C'est du bon travail. La chaîne fait un dernier tic.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11724,7 +12395,16 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Lila respire. Lila retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>maman|Oui.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|On cherche le seau.
+narrateur|On cherche le manteau.
+narrateur|On les prend.
+enfant-f|J'ai compris.
+papa|Bravo, Mila.
+maman|C'est du bon travail.
+narrateur|La chaîne fait un dernier tic.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11752,7 +12432,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Mila peut encore jouer, près des balançoires. Le ballon, le seau, ou le doudou ? Tu choisis. Après, on reprend tes affaires.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11916,7 +12596,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Mila peut encore jouer, près des balançoires.
+maman|Le ballon, le seau, ou le doudou ?
+papa|Tu choisis.
+papa|Après, on reprend tes affaires.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11944,7 +12627,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Près des balançoires, le ballon dort. Il est sous le siège. Il balance trop ? Non. Il reste là. Le seau est à tes pieds. Quand c'est l'heure, on cherche. On reprend tes affaires. Avant de partir. Je cherche. Puis on les prend. La chaîne fait un tic. Puis elle se tait. Tu as fini ce jeu ? Un tout petit peu. D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12084,7 +12767,21 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>narrateur|Près des balançoires, le ballon dort.
+narrateur|Il est sous le siège.
+enfant-f|Il balance trop ?
+maman|Non. Il reste là.
+papa|Le seau est à tes pieds.
+papa|Quand c'est l'heure, on cherche.
+maman|On reprend tes affaires.
+maman|Avant de partir.
+enfant-f|Je cherche.
+papa|Puis on les prend.
+narrateur|La chaîne fait un tic.
+narrateur|Puis elle se tait.
+maman|Tu as fini ce jeu ?
+enfant-f|Un tout petit peu.
+papa|D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12112,7 +12809,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire. Le manteau, le seau, ou le doudou ? On cherche. On prend. Reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12280,7 +12977,11 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire.
+maman|Le manteau, le seau, ou le doudou ?
+papa|On cherche. On prend.
+maman|Reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12308,7 +13009,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte les balançoires. Le ballon dort sous la balançoire. Mila cherche d'abord le manteau. Le manteau rouge est au banc. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend aussi le seau. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le soleil a quitté le tapis.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12448,7 +13149,25 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte les balançoires.
+narrateur|Le ballon dort sous la balançoire.
+narrateur|Mila cherche d'abord le manteau.
+narrateur|Le manteau rouge est au banc.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend aussi le seau.
+papa|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le soleil a quitté le tapis.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12476,7 +13195,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. La chaîne des balançoires se tait. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12616,7 +13335,14 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|La chaîne des balançoires se tait.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12644,7 +13370,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte les balançoires. Le ballon va, vient, tout doux. Mila cherche d'abord le seau. Le seau jaune sonne. On cherche. On prend. Je le prends. Bravo. Maintenant le manteau. Mila prend le manteau au banc. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le salon est un peu plus frais.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12784,7 +13510,25 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte les balançoires.
+narrateur|Le ballon va, vient, tout doux.
+narrateur|Mila cherche d'abord le seau.
+narrateur|Le seau jaune sonne.
+maman|On cherche. On prend.
+enfant-f|Je le prends.
+papa|Bravo. Maintenant le manteau.
+narrateur|Mila prend le manteau au banc.
+maman|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le salon est un peu plus frais.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12812,7 +13556,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. La chaîne des balançoires se tait. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12952,7 +13696,14 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|La chaîne des balançoires se tait.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12980,7 +13731,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. On entend un oiseau. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte les balançoires. Le ballon a un peu d'herbe. Mila cherche d'abord le doudou. Le doudou a une oreille dehors. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend le seau, puis le manteau. Tes affaires. J'ai tout. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. La porte du parc s'est tue.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13120,7 +13871,25 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. On entend un oiseau. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte les balançoires.
+narrateur|Le ballon a un peu d'herbe.
+narrateur|Mila cherche d'abord le doudou.
+narrateur|Le doudou a une oreille dehors.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend le seau, puis le manteau.
+papa|Tes affaires.
+enfant-f|J'ai tout.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|La porte du parc s'est tue.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13148,7 +13917,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. La chaîne des balançoires se tait. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13288,7 +14057,14 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|La chaîne des balançoires se tait.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13316,7 +14092,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+          <t>Près des balançoires, le seau attend. Il est au pied des chaînes. Il ne balance pas. Non. Il reste droit. Le manteau est au banc. Quand c'est l'heure, on cherche. On reprend tes affaires. Avant de partir. Je cherche. Puis on les prend. La chaîne fait un tic. Puis elle se tait. Tu as fini ce jeu ? Un tout petit peu. D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13456,7 +14232,21 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+          <t>narrateur|Près des balançoires, le seau attend.
+narrateur|Il est au pied des chaînes.
+enfant-f|Il ne balance pas.
+papa|Non. Il reste droit.
+maman|Le manteau est au banc.
+papa|Quand c'est l'heure, on cherche.
+maman|On reprend tes affaires.
+maman|Avant de partir.
+enfant-f|Je cherche.
+papa|Puis on les prend.
+narrateur|La chaîne fait un tic.
+narrateur|Puis elle se tait.
+maman|Tu as fini ce jeu ?
+enfant-f|Un tout petit peu.
+papa|D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13484,7 +14274,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire. Le manteau, le seau, ou le doudou ? On cherche. On prend. Reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13652,7 +14442,11 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire.
+maman|Le manteau, le seau, ou le doudou ?
+papa|On cherche. On prend.
+maman|Reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13680,7 +14474,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte les balançoires. Le seau est au pied des chaînes. Mila cherche d'abord le manteau. Le manteau rouge est au banc. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend aussi le seau. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le seau rentre avec Mila.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13820,7 +14614,25 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte les balançoires.
+narrateur|Le seau est au pied des chaînes.
+narrateur|Mila cherche d'abord le manteau.
+narrateur|Le manteau rouge est au banc.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend aussi le seau.
+papa|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le seau rentre avec Mila.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13848,7 +14660,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. La chaîne des balançoires se tait. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13988,7 +14800,14 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|La chaîne des balançoires se tait.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14016,7 +14835,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte les balançoires. Le seau ne balance pas. Mila cherche d'abord le seau. Le seau jaune sonne. On cherche. On prend. Je le prends. Bravo. Maintenant le manteau. Mila prend le manteau au banc. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le manteau rentre avec Mila.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14156,7 +14975,25 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte les balançoires.
+narrateur|Le seau ne balance pas.
+narrateur|Mila cherche d'abord le seau.
+narrateur|Le seau jaune sonne.
+maman|On cherche. On prend.
+enfant-f|Je le prends.
+papa|Bravo. Maintenant le manteau.
+narrateur|Mila prend le manteau au banc.
+maman|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le manteau rentre avec Mila.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14184,7 +15021,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. La chaîne des balançoires se tait. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14324,7 +15161,14 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|La chaîne des balançoires se tait.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14352,7 +15196,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte les balançoires. Le seau attend, bien droit. Mila cherche d'abord le doudou. Le doudou a une oreille dehors. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend le seau, puis le manteau. Tes affaires. J'ai tout. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le doudou rentre avec Mila.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14492,7 +15336,25 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte les balançoires.
+narrateur|Le seau attend, bien droit.
+narrateur|Mila cherche d'abord le doudou.
+narrateur|Le doudou a une oreille dehors.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend le seau, puis le manteau.
+papa|Tes affaires.
+enfant-f|J'ai tout.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le doudou rentre avec Mila.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14520,7 +15382,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. La chaîne des balançoires se tait. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14660,7 +15522,14 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|La chaîne des balançoires se tait.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14688,7 +15557,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Lila a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Près des balançoires, le doudou tient. Il a une place sur le siège. Avec moi. Avec toi, tout doux. Le seau reste en bas. Quand c'est l'heure, on cherche. On reprend tes affaires. Avant de partir. Je cherche. Puis on les prend. La chaîne fait un tic. Puis elle se tait. Tu as fini ce jeu ? Un tout petit peu. D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14828,7 +15697,21 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Lila a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Lila répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>narrateur|Près des balançoires, le doudou tient.
+narrateur|Il a une place sur le siège.
+enfant-f|Avec moi.
+maman|Avec toi, tout doux.
+papa|Le seau reste en bas.
+papa|Quand c'est l'heure, on cherche.
+maman|On reprend tes affaires.
+maman|Avant de partir.
+enfant-f|Je cherche.
+papa|Puis on les prend.
+narrateur|La chaîne fait un tic.
+narrateur|Puis elle se tait.
+maman|Tu as fini ce jeu ?
+enfant-f|Un tout petit peu.
+papa|D'accord. Puis tes affaires.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14856,7 +15739,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire. Le manteau, le seau, ou le doudou ? On cherche. On prend. Reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15024,7 +15907,11 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire.
+maman|Le manteau, le seau, ou le doudou ?
+papa|On cherche. On prend.
+maman|Reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15052,7 +15939,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Tom. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte les balançoires. Le doudou a une place sur le siège. Mila cherche d'abord le manteau. Le manteau rouge est au banc. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend aussi le seau. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le tapis rouge attend.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15192,7 +16079,25 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Tom. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte les balançoires.
+narrateur|Le doudou a une place sur le siège.
+narrateur|Mila cherche d'abord le manteau.
+narrateur|Le manteau rouge est au banc.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend aussi le seau.
+papa|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le tapis rouge attend.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15220,7 +16125,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. La chaîne des balançoires se tait. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15360,7 +16265,14 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|La chaîne des balançoires se tait.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15388,7 +16300,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Léa. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte les balançoires. Le doudou tient la chaîne, tout doux. Mila cherche d'abord le seau. Le seau jaune sonne. On cherche. On prend. Je le prends. Bravo. Maintenant le manteau. Mila prend le manteau au banc. Et le doudou. Il est là. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. Le fauteuil creux attend.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15528,7 +16440,25 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Léa. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte les balançoires.
+narrateur|Le doudou tient la chaîne, tout doux.
+narrateur|Mila cherche d'abord le seau.
+narrateur|Le seau jaune sonne.
+maman|On cherche. On prend.
+enfant-f|Je le prends.
+papa|Bravo. Maintenant le manteau.
+narrateur|Mila prend le manteau au banc.
+maman|Et le doudou.
+enfant-f|Il est là.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|Le fauteuil creux attend.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15556,7 +16486,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. La chaîne des balançoires se tait. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15696,7 +16626,14 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|La chaîne des balançoires se tait.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15724,7 +16661,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint Sami. Le vent est doux. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>Mila quitte les balançoires. Le doudou a le vent dans l'oreille. Mila cherche d'abord le doudou. Le doudou a une oreille dehors. On cherche. On prend. Je le prends. Bravo. Maintenant le seau. Mila prend le seau, puis le manteau. Tes affaires. J'ai tout. Reprendre ses affaires. Avant de partir. Mila a le seau. Mila a le manteau. Mila a le doudou. On rentre. Oui. Bravo. C'est du bon travail. La table est vide, maintenant.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15864,7 +16801,25 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Lila rejoint Sami. Le vent est doux. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Lila a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Lila a entendu : reprendre ses affaires, avant de partir. Lila dit merci à maman. On rentre.</t>
+          <t>narrateur|Mila quitte les balançoires.
+narrateur|Le doudou a le vent dans l'oreille.
+narrateur|Mila cherche d'abord le doudou.
+narrateur|Le doudou a une oreille dehors.
+papa|On cherche. On prend.
+enfant-f|Je le prends.
+maman|Bravo. Maintenant le seau.
+narrateur|Mila prend le seau, puis le manteau.
+papa|Tes affaires.
+enfant-f|J'ai tout.
+maman|Reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Mila a le seau.
+narrateur|Mila a le manteau.
+narrateur|Mila a le doudou.
+enfant-f|On rentre.
+maman|Oui. Bravo.
+papa|C'est du bon travail.
+narrateur|La table est vide, maintenant.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15892,7 +16847,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires. Mila reprend ses affaires. Avant de partir. Bravo, Mila. Tu as fait du bon travail. La chaîne des balançoires se tait. J'ai tout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16032,7 +16987,14 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires.
+narrateur|Mila reprend ses affaires.
+maman|Avant de partir.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|La chaîne des balançoires se tait.
+enfant-f|J'ai tout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16054,7 +17016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16148,6 +17110,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-038.xlsx
+++ b/stories/arbres/TREE-AUT-038.xlsx
@@ -1197,17 +1197,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le bois de la table fait tic au soleil. Il sèche, sans personne. Un pain tiède y pose son ventre. Ça sent la croûte, près du nez. Une mouche marche sur la mie. Mila pose sa joue sur le bois. Il est chaud, maman. Le pain vient du fournil. Un seau jaune attend près du pied. L'anse a un clou de cuivre. Le clou cligne, une fois. Tu as vu ce clou, Mila ? Il brille, papa. En ce moment, Mila veut le bac. Un gâteau de sable, vite ! Elle tire le seau par l'anse. Un pigeon se pose sur le pain. Il pique une miette, nette. Oh ! Mila sursaute. Le seau roule sous la table. Toc, contre le pied de bois. Le clou de cuivre s'éteint, à l'ombre. Il reste là, à l'abri. On y va ? Mila pousse le seau plus loin. Il ne roule plus. Elle part, les mains vides.</t>
+          <t>Le bois de la table fait tic au soleil. Il sèche, sans personne. Un pain tiède y pose son ventre. Ça sent la croûte, près du nez. Une mouche marche sur la mie. Mila pose sa joue sur le bois. Il est chaud, maman. Le pain vient du fournil. Un seau jaune attend près du pied. L'anse a un clou de cuivre. Le clou cligne, une fois. Tu as vu ce clou, Mila ? Il brille, papa. En ce moment, Mila veut le bac. Un gâteau de sable, vite ! Elle tire le seau par l'anse. Un pigeon se pose sur le pain. Il pique une miette, nette. Oh ! Mila sursaute. Le seau roule sous la table. Toc, contre le pied de bois. Le clou de cuivre s'éteint, à l'ombre. Une miette reste collée à l'anse. Il reste là, à l'abri. On y va ? Mila pousse le seau plus loin. Il ne roule plus. Elle part, les mains vides.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le bois de la table fait tic au soleil. Il sèche, sans personne. Un pain tiède y pose son ventre. Ça sent la croûte, près du nez. Une mouche marche sur la mie. Mila pose sa joue sur le bois. Il est chaud, maman. Le pain vient du fournil. Un seau jaune attend près du pied. L'anse a un &lt;emphasis level="moderate"&gt;clou de cuivre&lt;/emphasis&gt;. Le clou cligne, une fois. Tu as vu ce clou, Mila ? Il brille, papa. En ce moment, Mila veut le bac. Un gâteau de sable, vite ! Elle tire le seau par l'anse. Un pigeon se pose sur le pain. Il pique une miette, nette. Oh ! Mila sursaute. Le seau roule sous la table. Toc, contre le pied de bois. Le clou de cuivre s'éteint, à l'ombre. Il reste là, à l'abri. On y va ? Mila pousse le seau plus loin. Il ne roule plus. Elle part, les mains vides.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le bois de la table fait tic au soleil. Il sèche, sans personne. Un pain tiède y pose son ventre. Ça sent la croûte, près du nez. Une mouche marche sur la mie. Mila pose sa joue sur le bois. Il est chaud, maman. Le pain vient du fournil. Un seau jaune attend près du pied. L'anse a un &lt;emphasis level="moderate"&gt;clou de cuivre&lt;/emphasis&gt;. Le clou cligne, une fois. Tu as vu ce clou, Mila ? Il brille, papa. En ce moment, Mila veut le bac. Un gâteau de sable, vite ! Elle tire le seau par l'anse. Un pigeon se pose sur le pain. Il pique une miette, nette. Oh ! Mila sursaute. Le seau roule sous la table. Toc, contre le pied de bois. Le clou de cuivre s'éteint, à l'ombre. Une miette reste collée à l'anse. Il reste là, à l'abri. On y va ? Mila pousse le seau plus loin. Il ne roule plus. Elle part, les mains vides.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Le bois de la table fait tic au soleil. Il sèche, sans personne. Un pain tiède y pose son ventre. Ça sent la croûte, près du nez. Une mouche marche sur la mie. Mila pose sa joue sur le bois. Il est chaud, maman. Le pain vient du fournil. Un seau jaune attend près du pied. L'anse a un &lt;emphasis&gt;clou de cuivre&lt;/emphasis&gt;. Le clou cligne, une fois. Tu as vu ce clou, Mila ? Il brille, papa. En ce moment, Mila veut le bac. Un gâteau de sable, vite ! Elle tire le seau par l'anse. Un pigeon se pose sur le pain. Il pique une miette, nette. Oh ! Mila sursaute. Le seau roule sous la table. Toc, contre le pied de bois. Le clou de cuivre s'éteint, à l'ombre. Il reste là, à l'abri. On y va ? Mila pousse le seau plus loin. Il ne roule plus. Elle part, les mains vides. [pause]</t>
+          <t>Le bois de la table fait tic au soleil. Il sèche, sans personne. Un pain tiède y pose son ventre. Ça sent la croûte, près du nez. Une mouche marche sur la mie. Mila pose sa joue sur le bois. Il est chaud, maman. Le pain vient du fournil. Un seau jaune attend près du pied. L'anse a un &lt;emphasis&gt;clou de cuivre&lt;/emphasis&gt;. Le clou cligne, une fois. Tu as vu ce clou, Mila ? Il brille, papa. En ce moment, Mila veut le bac. Un gâteau de sable, vite ! Elle tire le seau par l'anse. Un pigeon se pose sur le pain. Il pique une miette, nette. Oh ! Mila sursaute. Le seau roule sous la table. Toc, contre le pied de bois. Le clou de cuivre s'éteint, à l'ombre. Une miette reste collée à l'anse. Il reste là, à l'abri. On y va ? Mila pousse le seau plus loin. Il ne roule plus. Elle part, les mains vides. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1364,6 +1364,7 @@
 narrateur|Le seau roule sous la table.
 narrateur|Toc, contre le pied de bois.
 narrateur|Le clou de cuivre s'éteint, à l'ombre.
+narrateur|Une miette reste collée à l'anse.
 enfant-f|Il reste là, à l'abri.
 papa|On y va ?
 narrateur|Mila pousse le seau plus loin.
@@ -1603,17 +1604,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila s'agenouille près du bac. Le sable est frais, un peu fin. Il coule entre ses doigts. Un gâteau, maman. Avec tes mains ? Avec le seau ! Elle court vers la table. Elle tire l'anse, trop fort. L'anse bute contre le pied. Il ne vient pas. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. On s'accroupit ? Papa se met à sa hauteur. Le clou, il est où ? Tu l'as vu, au départ.</t>
+          <t>Mila s'agenouille près du bac. Le sable est frais, un peu fin. Il coule entre ses doigts. Un gâteau, maman. Avec tes mains ? Avec le seau ! Elle court vers la table. Elle tire l'anse, trop fort. L'anse bute contre le pied. Le seau recule, dans l'ombre. Il ne vient pas. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. On s'accroupit ? Papa se met à sa hauteur. Le clou, il est où ? Tu l'as vu, au départ.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila s'agenouille près du bac. Le sable est frais, un peu fin. Il coule entre ses doigts. Un &lt;emphasis level="moderate"&gt;gâteau&lt;/emphasis&gt;, maman. Avec tes mains ? Avec le seau ! Elle court vers la table. Elle tire l'anse, trop fort. L'anse bute contre le pied. Il ne vient pas. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. On s'accroupit ? Papa se met à sa hauteur. Le clou, il est où ? Tu l'as vu, au départ.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila s'agenouille près du bac. Le sable est frais, un peu fin. Il coule entre ses doigts. Un &lt;emphasis level="moderate"&gt;gâteau&lt;/emphasis&gt;, maman. Avec tes mains ? Avec le seau ! Elle court vers la table. Elle tire l'anse, trop fort. L'anse bute contre le pied. Le seau recule, dans l'ombre. Il ne vient pas. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. On s'accroupit ? Papa se met à sa hauteur. Le clou, il est où ? Tu l'as vu, au départ.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Mila s'agenouille près du bac. Le sable est frais, un peu fin. Il coule entre ses doigts. Un &lt;emphasis&gt;gâteau&lt;/emphasis&gt;, maman. Avec tes mains ? Avec le seau ! Elle court vers la table. Elle tire l'anse, trop fort. L'anse bute contre le pied. Il ne vient pas. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. On s'accroupit ? Papa se met à sa hauteur. Le clou, il est où ? Tu l'as vu, au départ. [pause]</t>
+          <t>Mila s'agenouille près du bac. Le sable est frais, un peu fin. Il coule entre ses doigts. Un &lt;emphasis&gt;gâteau&lt;/emphasis&gt;, maman. Avec tes mains ? Avec le seau ! Elle court vers la table. Elle tire l'anse, trop fort. L'anse bute contre le pied. Le seau recule, dans l'ombre. Il ne vient pas. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. On s'accroupit ? Papa se met à sa hauteur. Le clou, il est où ? Tu l'as vu, au départ. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1756,6 +1757,7 @@
 narrateur|Elle court vers la table.
 narrateur|Elle tire l'anse, trop fort.
 narrateur|L'anse bute contre le pied.
+narrateur|Le seau recule, dans l'ombre.
 enfant-f|Il ne vient pas.
 narrateur|Le sourire de Mila disparaît.
 narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
@@ -2363,17 +2365,17 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Près du bac, le ballon rouge attend. Il est lisse, un peu frais. Il pousse le sable ! Mila frappe trop fort. Le ballon file sous la table. Le seau aussi ? Elle se jette à plat ventre. Sa main trouve le cuir rouge. Pas l'anse. Ce n'est pas lui. La serviette du pain tombe, large. Elle cache le clou de cuivre. On tire tout ? Non. Mila refuse de foncer. Elle écoute le square. Toc, très loin, sous le bois. Le clou. Tu l'as entendu, toi.</t>
+          <t>Près du bac, le ballon rouge attend. Il est lisse, un peu frais. Il pousse le sable ! Mila frappe trop fort. Le ballon file sous la table. Le seau aussi ? Elle se jette à plat ventre. Sa main trouve le cuir rouge. Pas l'anse. Ce n'est pas lui. La serviette du pain tombe, large. Elle cache le clou de cuivre. On tire tout ? Non. Mila refuse de foncer. Elle écoute le square. Le pigeon reprend une miette, loin. C'est l'heure, presque. Pas sans le toc. Toc, très loin, sous le bois. Le clou. Tu l'as entendu, toi.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Près du bac, le ballon rouge attend. Il est lisse, un peu frais. Il pousse le sable ! Mila frappe trop fort. Le ballon file sous la table. Le seau aussi ? Elle se jette à plat ventre. Sa main trouve le cuir rouge. Pas l'anse. Ce n'est pas lui. La serviette du pain tombe, large. Elle cache le clou de cuivre. On tire tout ? Non. Mila refuse de foncer. Elle écoute le square. Toc, très loin, sous le bois. Le clou. Tu l'as entendu, toi.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Près du bac, le ballon rouge attend. Il est lisse, un peu frais. Il pousse le sable ! Mila frappe trop fort. Le ballon file sous la table. Le seau aussi ? Elle se jette à plat ventre. Sa main trouve le cuir rouge. Pas l'anse. Ce n'est pas lui. La serviette du pain tombe, large. Elle cache le clou de cuivre. On tire tout ? Non. Mila refuse de foncer. Elle écoute le square. Le pigeon reprend une miette, loin. C'est l'heure, presque. Pas sans le toc. Toc, très loin, sous le bois. Le clou. Tu l'as entendu, toi.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Près du bac, le ballon rouge attend. Il est lisse, un peu frais. Il pousse le sable ! Mila frappe trop fort. Le ballon file sous la table. Le seau aussi ? Elle se jette à plat ventre. Sa main trouve le cuir rouge. Pas l'anse. Ce n'est pas lui. La serviette du pain tombe, large. Elle cache le clou de cuivre. On tire tout ? Non. Mila refuse de foncer. Elle écoute le square. Toc, très loin, sous le bois. Le clou. Tu l'as entendu, toi.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Près du bac, le ballon rouge attend. Il est lisse, un peu frais. Il pousse le sable ! Mila frappe trop fort. Le ballon file sous la table. Le seau aussi ? Elle se jette à plat ventre. Sa main trouve le cuir rouge. Pas l'anse. Ce n'est pas lui. La serviette du pain tombe, large. Elle cache le clou de cuivre. On tire tout ? Non. Mila refuse de foncer. Elle écoute le square. Le pigeon reprend une miette, loin. C'est l'heure, presque. Pas sans le toc. Toc, très loin, sous le bois. Le clou. Tu l'as entendu, toi.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -2527,6 +2529,9 @@
 enfant-f|Non.
 narrateur|Mila refuse de foncer.
 narrateur|Elle écoute le square.
+narrateur|Le pigeon reprend une miette, loin.
+papa|C'est l'heure, presque.
+enfant-f|Pas sans le toc.
 narrateur|Toc, très loin, sous le bois.
 enfant-f|Le clou.
 maman|Tu l'as entendu, toi.</t>
@@ -3899,17 +3904,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Mila revient vers la table. L'ombre sous le plateau est froide. Le seau, maman. Elle tire l'anse d'un coup. L'anse bute, sèche, contre le pied. Il reste. La serviette glisse du pain. Elle tombe comme un rideau. Le clou de cuivre disparaît. Je n'aime pas ça. On s'accroupit ? Maman se met à sa hauteur. Je tire, moi ? Non. Mila refuse de foncer. Elle observe le seau, dans le noir. Elle écoute le bois. Le toc du clou. Tu l'as, ce son.</t>
+          <t>Mila revient vers la table. L'ombre sous le plateau est froide. Le seau, maman. Elle tire l'anse d'un coup. L'anse bute, sèche, contre le pied. Il reste. La serviette glisse du pain. Elle tombe comme un rideau. Le clou de cuivre disparaît. Je n'aime pas ça. On s'accroupit ? Maman se met à sa hauteur. Je tire, moi ? Non. Mila refuse de foncer. Elle observe le seau, dans le noir. Elle écoute le bois. C'est l'heure, presque. Pas sans le toc. Le toc du clou. Tu l'as, ce son.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Mila revient vers la table. L'ombre sous le plateau est froide. Le seau, maman. Elle tire l'anse d'un coup. L'anse bute, sèche, contre le pied. Il reste. La serviette glisse du pain. Elle tombe comme un rideau. Le clou de cuivre disparaît. Je n'aime pas ça. On s'accroupit ? Maman se met à sa hauteur. Je tire, moi ? Non. Mila refuse de foncer. Elle observe le seau, dans le noir. Elle écoute le bois. Le toc du clou. Tu l'as, ce son.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Mila revient vers la table. L'ombre sous le plateau est froide. Le seau, maman. Elle tire l'anse d'un coup. L'anse bute, sèche, contre le pied. Il reste. La serviette glisse du pain. Elle tombe comme un rideau. Le clou de cuivre disparaît. Je n'aime pas ça. On s'accroupit ? Maman se met à sa hauteur. Je tire, moi ? Non. Mila refuse de foncer. Elle observe le seau, dans le noir. Elle écoute le bois. C'est l'heure, presque. Pas sans le toc. Le toc du clou. Tu l'as, ce son.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Mila revient vers la table. L'ombre sous le plateau est froide. Le seau, maman. Elle tire l'anse d'un coup. L'anse bute, sèche, contre le pied. Il reste. La serviette glisse du pain. Elle tombe comme un rideau. Le clou de cuivre disparaît. Je n'aime pas ça. On s'accroupit ? Maman se met à sa hauteur. Je tire, moi ? Non. Mila refuse de foncer. Elle observe le seau, dans le noir. Elle écoute le bois. Le toc du clou. Tu l'as, ce son.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Mila revient vers la table. L'ombre sous le plateau est froide. Le seau, maman. Elle tire l'anse d'un coup. L'anse bute, sèche, contre le pied. Il reste. La serviette glisse du pain. Elle tombe comme un rideau. Le clou de cuivre disparaît. Je n'aime pas ça. On s'accroupit ? Maman se met à sa hauteur. Je tire, moi ? Non. Mila refuse de foncer. Elle observe le seau, dans le noir. Elle écoute le bois. C'est l'heure, presque. Pas sans le toc. Le toc du clou. Tu l'as, ce son.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -4064,6 +4069,8 @@
 narrateur|Mila refuse de foncer.
 narrateur|Elle observe le seau, dans le noir.
 narrateur|Elle écoute le bois.
+papa|C'est l'heure, presque.
+enfant-f|Pas sans le toc.
 enfant-f|Le toc du clou.
 papa|Tu l'as, ce son.</t>
         </is>
@@ -5431,17 +5438,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Près du bac, le doudou gris attend. Le tissu est chaud, un peu lourd. Il voit sous la table. Mila le serre trop fort. L'oreille grise cache l'ombre. Elle cherche l'anse, à l'aveugle. Sa main trouve le banc, pas le seau. Il n'est pas là. Le sourire de Mila reste bas. L'oreille, un peu de côté ? Papa se met à sa hauteur. J'attends. Mila refuse de foncer. Elle écarte l'oreille, lentement. Un toc minuscule, sous le bois. Le clou. Tu l'as entendu, seule. Un grain colle à l'oreille grise.</t>
+          <t>Près du bac, le doudou gris attend. Le tissu est chaud, un peu lourd. Il voit sous la table. Mila le serre trop fort. L'oreille grise cache l'ombre. Elle cherche l'anse, à l'aveugle. Sa main trouve le banc, pas le seau. Il n'est pas là. Le sourire de Mila reste bas. L'oreille, un peu de côté ? Papa se met à sa hauteur. J'attends. Mila refuse de foncer. Elle écarte l'oreille, lentement. C'est l'heure, presque. Pas sans le toc. Un toc minuscule, sous le bois. Le clou. Tu l'as entendu, seule. Un grain colle à l'oreille grise.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Près du bac, le doudou gris attend. Le tissu est chaud, un peu lourd. Il voit sous la table. Mila le serre trop fort. L'oreille grise cache l'ombre. Elle cherche l'anse, à l'aveugle. Sa main trouve le banc, pas le seau. Il n'est pas là. Le sourire de Mila reste bas. L'oreille, un peu de côté ? Papa se met à sa hauteur. J'attends. Mila refuse de foncer. Elle écarte l'oreille, lentement. Un toc minuscule, sous le bois. Le clou. Tu l'as entendu, seule. Un grain colle à l'oreille grise.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Près du bac, le doudou gris attend. Le tissu est chaud, un peu lourd. Il voit sous la table. Mila le serre trop fort. L'oreille grise cache l'ombre. Elle cherche l'anse, à l'aveugle. Sa main trouve le banc, pas le seau. Il n'est pas là. Le sourire de Mila reste bas. L'oreille, un peu de côté ? Papa se met à sa hauteur. J'attends. Mila refuse de foncer. Elle écarte l'oreille, lentement. C'est l'heure, presque. Pas sans le toc. Un toc minuscule, sous le bois. Le clou. Tu l'as entendu, seule. Un grain colle à l'oreille grise.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Près du bac, le doudou gris attend. Le tissu est chaud, un peu lourd. Il voit sous la table. Mila le serre trop fort. L'oreille grise cache l'ombre. Elle cherche l'anse, à l'aveugle. Sa main trouve le banc, pas le seau. Il n'est pas là. Le sourire de Mila reste bas. L'oreille, un peu de côté ? Papa se met à sa hauteur. J'attends. Mila refuse de foncer. Elle écarte l'oreille, lentement. Un toc minuscule, sous le bois. Le clou. Tu l'as entendu, seule. Un grain colle à l'oreille grise.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Près du bac, le doudou gris attend. Le tissu est chaud, un peu lourd. Il voit sous la table. Mila le serre trop fort. L'oreille grise cache l'ombre. Elle cherche l'anse, à l'aveugle. Sa main trouve le banc, pas le seau. Il n'est pas là. Le sourire de Mila reste bas. L'oreille, un peu de côté ? Papa se met à sa hauteur. J'attends. Mila refuse de foncer. Elle écarte l'oreille, lentement. C'est l'heure, presque. Pas sans le toc. Un toc minuscule, sous le bois. Le clou. Tu l'as entendu, seule. Un grain colle à l'oreille grise.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -5593,6 +5600,8 @@
 enfant-f|J'attends.
 narrateur|Mila refuse de foncer.
 narrateur|Elle écarte l'oreille, lentement.
+papa|C'est l'heure, presque.
+enfant-f|Pas sans le toc.
 narrateur|Un toc minuscule, sous le bois.
 enfant-f|Le clou.
 maman|Tu l'as entendu, seule.
@@ -6958,17 +6967,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Mila grimpe la marche du toboggan. Le plastique est lisse, un peu froid. Une miette de pain y colle. Le seau glisse avec moi ! Il est où, ce seau ? Je le prends. Elle redescend, trop vite. Elle tire l'anse sous le bois. L'anse bute, sèche. Zut. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Je m'accroupis, d'accord ? Maman se met à sa hauteur. Le clou ne cligne plus. Tu l'as vu, toi.</t>
+          <t>Mila grimpe la marche du toboggan. Le plastique est lisse, un peu froid. Une miette de pain y colle. Le seau glisse avec moi ! Il est où, ce seau ? Je le prends. Elle redescend, trop vite. Elle tire l'anse sous le bois. L'anse bute, sèche. Le seau recule, dans l'ombre. Zut. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Je m'accroupis, d'accord ? Maman se met à sa hauteur. Le clou ne cligne plus. Tu l'as vu, toi.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila grimpe la marche du toboggan. Le plastique est lisse, un peu froid. Une miette de pain y colle. Le seau glisse avec moi ! Il est où, ce seau ? Je le prends. Elle redescend, trop vite. Elle tire l'anse sous le bois. L'anse bute, sèche. Zut. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Je m'accroupis, d'accord ? Maman se met à sa hauteur. Le clou ne cligne plus. Tu l'as vu, toi.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila grimpe la marche du toboggan. Le plastique est lisse, un peu froid. Une miette de pain y colle. Le seau glisse avec moi ! Il est où, ce seau ? Je le prends. Elle redescend, trop vite. Elle tire l'anse sous le bois. L'anse bute, sèche. Le seau recule, dans l'ombre. Zut. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Je m'accroupis, d'accord ? Maman se met à sa hauteur. Le clou ne cligne plus. Tu l'as vu, toi.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Mila grimpe la marche du toboggan. Le plastique est lisse, un peu froid. Une miette de pain y colle. Le seau glisse avec moi ! Il est où, ce seau ? Je le prends. Elle redescend, trop vite. Elle tire l'anse sous le bois. L'anse bute, sèche. Zut. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Je m'accroupis, d'accord ? Maman se met à sa hauteur. Le clou ne cligne plus. Tu l'as vu, toi. [pause]</t>
+          <t>Mila grimpe la marche du toboggan. Le plastique est lisse, un peu froid. Une miette de pain y colle. Le seau glisse avec moi ! Il est où, ce seau ? Je le prends. Elle redescend, trop vite. Elle tire l'anse sous le bois. L'anse bute, sèche. Le seau recule, dans l'ombre. Zut. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Je m'accroupis, d'accord ? Maman se met à sa hauteur. Le clou ne cligne plus. Tu l'as vu, toi. [pause]</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -7111,6 +7120,7 @@
 narrateur|Elle redescend, trop vite.
 narrateur|Elle tire l'anse sous le bois.
 narrateur|L'anse bute, sèche.
+narrateur|Le seau recule, dans l'ombre.
 enfant-f|Zut.
 narrateur|Le sourire de Mila disparaît.
 narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
@@ -7718,17 +7728,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Au pied du toboggan, le ballon attend. Il est froid, près de la rampe. Il roule jusqu'au seau ! Mila le lance trop fort. Le ballon tape le pied de table. Il rebondit, puis se cache. Avec le seau ? Elle rampe. Sa main attrape le cuir, pas l'anse. Faux. Une miette de marche tombe, large. Elle colle au clou de cuivre. On chasse tout ? Non. Mila refuse de foncer. Elle écoute le square. Toc, sous le plastique et le bois. Le clou est là. Tu l'as trouvé, ce son.</t>
+          <t>Au pied du toboggan, le ballon attend. Il est froid, près de la rampe. Il roule jusqu'au seau ! Mila le lance trop fort. Le ballon tape le pied de table. Il rebondit, puis se cache. Avec le seau ? Elle rampe. Sa main attrape le cuir, pas l'anse. Faux. Une miette de marche tombe, large. Elle colle au clou de cuivre. On chasse tout ? Non. Mila refuse de foncer. Elle écoute le square. C'est l'heure, presque. Pas sans le toc. Toc, sous le plastique et le bois. Le clou est là. Tu l'as trouvé, ce son.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Au pied du toboggan, le ballon attend. Il est froid, près de la rampe. Il roule jusqu'au seau ! Mila le lance trop fort. Le ballon tape le pied de table. Il rebondit, puis se cache. Avec le seau ? Elle rampe. Sa main attrape le cuir, pas l'anse. Faux. Une miette de marche tombe, large. Elle colle au clou de cuivre. On chasse tout ? Non. Mila refuse de foncer. Elle écoute le square. Toc, sous le plastique et le bois. Le clou est là. Tu l'as trouvé, ce son.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Au pied du toboggan, le ballon attend. Il est froid, près de la rampe. Il roule jusqu'au seau ! Mila le lance trop fort. Le ballon tape le pied de table. Il rebondit, puis se cache. Avec le seau ? Elle rampe. Sa main attrape le cuir, pas l'anse. Faux. Une miette de marche tombe, large. Elle colle au clou de cuivre. On chasse tout ? Non. Mila refuse de foncer. Elle écoute le square. C'est l'heure, presque. Pas sans le toc. Toc, sous le plastique et le bois. Le clou est là. Tu l'as trouvé, ce son.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Au pied du toboggan, le ballon attend. Il est froid, près de la rampe. Il roule jusqu'au seau ! Mila le lance trop fort. Le ballon tape le pied de table. Il rebondit, puis se cache. Avec le seau ? Elle rampe. Sa main attrape le cuir, pas l'anse. Faux. Une miette de marche tombe, large. Elle colle au clou de cuivre. On chasse tout ? Non. Mila refuse de foncer. Elle écoute le square. Toc, sous le plastique et le bois. Le clou est là. Tu l'as trouvé, ce son.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Au pied du toboggan, le ballon attend. Il est froid, près de la rampe. Il roule jusqu'au seau ! Mila le lance trop fort. Le ballon tape le pied de table. Il rebondit, puis se cache. Avec le seau ? Elle rampe. Sa main attrape le cuir, pas l'anse. Faux. Une miette de marche tombe, large. Elle colle au clou de cuivre. On chasse tout ? Non. Mila refuse de foncer. Elle écoute le square. C'est l'heure, presque. Pas sans le toc. Toc, sous le plastique et le bois. Le clou est là. Tu l'as trouvé, ce son.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -7882,6 +7892,8 @@
 enfant-f|Non.
 narrateur|Mila refuse de foncer.
 narrateur|Elle écoute le square.
+maman|C'est l'heure, presque.
+enfant-f|Pas sans le toc.
 narrateur|Toc, sous le plastique et le bois.
 enfant-f|Le clou est là.
 papa|Tu l'as trouvé, ce son.</t>
@@ -9248,17 +9260,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Mila revient vers la table. Une miette brille sur la marche. Le seau, papa. Elle tire, trop vite. L'anse bute, sèche. Le seau penche, puis recule. Il ne veut pas. La serviette du pain tombe. Elle cache le clou de cuivre. Un coup sec ? Non. Mila refuse de foncer. Maman se met à sa hauteur. Personne ne dit le lieu. Mila observe le seau, dans l'ombre. Elle écoute le bois. Le toc du clou. Tu l'as, ce bruit. La miette reste sur le plastique.</t>
+          <t>Mila revient vers la table. Une miette brille sur la marche. Le seau, papa. Elle tire, trop vite. L'anse bute, sèche. Le seau penche, puis recule. Il ne veut pas. La serviette du pain tombe. Elle cache le clou de cuivre. Un coup sec ? Non. Mila refuse de foncer. Maman se met à sa hauteur. Personne ne dit le lieu. Mila observe le seau, dans l'ombre. Elle écoute le bois. C'est l'heure, presque. Pas sans le toc. Le toc du clou. Tu l'as, ce bruit. La miette reste sur le plastique.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Mila revient vers la table. Une miette brille sur la marche. Le seau, papa. Elle tire, trop vite. L'anse bute, sèche. Le seau penche, puis recule. Il ne veut pas. La serviette du pain tombe. Elle cache le clou de cuivre. Un coup sec ? Non. Mila refuse de foncer. Maman se met à sa hauteur. Personne ne dit le lieu. Mila observe le seau, dans l'ombre. Elle écoute le bois. Le toc du clou. Tu l'as, ce bruit. La miette reste sur le plastique.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Mila revient vers la table. Une miette brille sur la marche. Le seau, papa. Elle tire, trop vite. L'anse bute, sèche. Le seau penche, puis recule. Il ne veut pas. La serviette du pain tombe. Elle cache le clou de cuivre. Un coup sec ? Non. Mila refuse de foncer. Maman se met à sa hauteur. Personne ne dit le lieu. Mila observe le seau, dans l'ombre. Elle écoute le bois. C'est l'heure, presque. Pas sans le toc. Le toc du clou. Tu l'as, ce bruit. La miette reste sur le plastique.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Mila revient vers la table. Une miette brille sur la marche. Le seau, papa. Elle tire, trop vite. L'anse bute, sèche. Le seau penche, puis recule. Il ne veut pas. La serviette du pain tombe. Elle cache le clou de cuivre. Un coup sec ? Non. Mila refuse de foncer. Maman se met à sa hauteur. Personne ne dit le lieu. Mila observe le seau, dans l'ombre. Elle écoute le bois. Le toc du clou. Tu l'as, ce bruit. La miette reste sur le plastique.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Mila revient vers la table. Une miette brille sur la marche. Le seau, papa. Elle tire, trop vite. L'anse bute, sèche. Le seau penche, puis recule. Il ne veut pas. La serviette du pain tombe. Elle cache le clou de cuivre. Un coup sec ? Non. Mila refuse de foncer. Maman se met à sa hauteur. Personne ne dit le lieu. Mila observe le seau, dans l'ombre. Elle écoute le bois. C'est l'heure, presque. Pas sans le toc. Le toc du clou. Tu l'as, ce bruit. La miette reste sur le plastique.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -9412,6 +9424,8 @@
 narrateur|Personne ne dit le lieu.
 narrateur|Mila observe le seau, dans l'ombre.
 narrateur|Elle écoute le bois.
+papa|C'est l'heure, presque.
+enfant-f|Pas sans le toc.
 enfant-f|Le toc du clou.
 maman|Tu l'as, ce bruit.
 narrateur|La miette reste sur le plastique.</t>
@@ -10778,17 +10792,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Au toboggan, le doudou a vu la rampe. L'oreille grise est un peu froide. Il attrape le seau, en bas. Mila glisse le doudou sous le bois. Le tissu s'accroche au pied. L'anse reste loin. Il est coincé, lui. Le sourire de Mila disparaît. On tire le tissu ? Doucement. Mila refuse de foncer. Elle recule le doudou, un pouce. Puis un autre. Un toc minuscule, sous le plateau. Le clou. Tu l'as entendu, seule. Papa se met à sa hauteur. Une miette colle au ventre gris.</t>
+          <t>Au toboggan, le doudou a vu la rampe. L'oreille grise est un peu froide. Il attrape le seau, en bas. Mila glisse le doudou sous le bois. Le tissu s'accroche au pied. L'anse reste loin. Il est coincé, lui. Le sourire de Mila disparaît. On tire le tissu ? Doucement. Mila refuse de foncer. Elle recule le doudou, un pouce. Puis un autre. C'est l'heure, presque. Pas sans le toc. Un toc minuscule, sous le plateau. Le clou. Tu l'as entendu, seule. Papa se met à sa hauteur. Une miette colle au ventre gris.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Au toboggan, le doudou a vu la rampe. L'oreille grise est un peu froide. Il attrape le seau, en bas. Mila glisse le doudou sous le bois. Le tissu s'accroche au pied. L'anse reste loin. Il est coincé, lui. Le sourire de Mila disparaît. On tire le tissu ? Doucement. Mila refuse de foncer. Elle recule le doudou, un pouce. Puis un autre. Un toc minuscule, sous le plateau. Le clou. Tu l'as entendu, seule. Papa se met à sa hauteur. Une miette colle au ventre gris.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Au toboggan, le doudou a vu la rampe. L'oreille grise est un peu froide. Il attrape le seau, en bas. Mila glisse le doudou sous le bois. Le tissu s'accroche au pied. L'anse reste loin. Il est coincé, lui. Le sourire de Mila disparaît. On tire le tissu ? Doucement. Mila refuse de foncer. Elle recule le doudou, un pouce. Puis un autre. C'est l'heure, presque. Pas sans le toc. Un toc minuscule, sous le plateau. Le clou. Tu l'as entendu, seule. Papa se met à sa hauteur. Une miette colle au ventre gris.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Au toboggan, le doudou a vu la rampe. L'oreille grise est un peu froide. Il attrape le seau, en bas. Mila glisse le doudou sous le bois. Le tissu s'accroche au pied. L'anse reste loin. Il est coincé, lui. Le sourire de Mila disparaît. On tire le tissu ? Doucement. Mila refuse de foncer. Elle recule le doudou, un pouce. Puis un autre. Un toc minuscule, sous le plateau. Le clou. Tu l'as entendu, seule. Papa se met à sa hauteur. Une miette colle au ventre gris.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Au toboggan, le doudou a vu la rampe. L'oreille grise est un peu froide. Il attrape le seau, en bas. Mila glisse le doudou sous le bois. Le tissu s'accroche au pied. L'anse reste loin. Il est coincé, lui. Le sourire de Mila disparaît. On tire le tissu ? Doucement. Mila refuse de foncer. Elle recule le doudou, un pouce. Puis un autre. C'est l'heure, presque. Pas sans le toc. Un toc minuscule, sous le plateau. Le clou. Tu l'as entendu, seule. Papa se met à sa hauteur. Une miette colle au ventre gris.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -10939,6 +10953,8 @@
 narrateur|Mila refuse de foncer.
 narrateur|Elle recule le doudou, un pouce.
 narrateur|Puis un autre.
+papa|C'est l'heure, presque.
+enfant-f|Pas sans le toc.
 narrateur|Un toc minuscule, sous le plateau.
 enfant-f|Le clou.
 maman|Tu l'as entendu, seule.
@@ -12305,17 +12321,17 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Mila va vers les balançoires. Une chaîne fait tic, mince. Le siège rouge est tiède. Le seau s'assoit avec moi. Il est resté où ? Je le cherche. Elle court, les mains ouvertes. Elle tire l'anse d'un coup. L'anse bute contre le pied. Il reste coincé. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. On s'accroupit ? Papa se met à sa hauteur. Le clou, il s'est tu. Tu l'as entendu, au départ.</t>
+          <t>Mila va vers les balançoires. Une chaîne fait tic, mince. Le siège rouge est tiède. Le seau s'assoit avec moi. Il est resté où ? Je le cherche. Elle court, les mains ouvertes. Elle tire l'anse d'un coup. L'anse bute contre le pied. Le seau recule, dans l'ombre. Il reste coincé. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. On s'accroupit ? Papa se met à sa hauteur. Le clou, il s'est tu. Tu l'as entendu, au départ.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila va vers les balançoires. Une chaîne fait tic, mince. Le siège rouge est tiède. Le seau s'assoit avec moi. Il est resté où ? Je le cherche. Elle court, les mains ouvertes. Elle tire l'anse d'un coup. L'anse bute contre le pied. Il reste coincé. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. On s'accroupit ? Papa se met à sa hauteur. Le clou, il s'est tu. Tu l'as entendu, au départ.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila va vers les balançoires. Une chaîne fait tic, mince. Le siège rouge est tiède. Le seau s'assoit avec moi. Il est resté où ? Je le cherche. Elle court, les mains ouvertes. Elle tire l'anse d'un coup. L'anse bute contre le pied. Le seau recule, dans l'ombre. Il reste coincé. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. On s'accroupit ? Papa se met à sa hauteur. Le clou, il s'est tu. Tu l'as entendu, au départ.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Mila va vers les balançoires. Une chaîne fait tic, mince. Le siège rouge est tiède. Le seau s'assoit avec moi. Il est resté où ? Je le cherche. Elle court, les mains ouvertes. Elle tire l'anse d'un coup. L'anse bute contre le pied. Il reste coincé. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. On s'accroupit ? Papa se met à sa hauteur. Le clou, il s'est tu. Tu l'as entendu, au départ. [pause]</t>
+          <t>Mila va vers les balançoires. Une chaîne fait tic, mince. Le siège rouge est tiède. Le seau s'assoit avec moi. Il est resté où ? Je le cherche. Elle court, les mains ouvertes. Elle tire l'anse d'un coup. L'anse bute contre le pied. Le seau recule, dans l'ombre. Il reste coincé. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. On s'accroupit ? Papa se met à sa hauteur. Le clou, il s'est tu. Tu l'as entendu, au départ. [pause]</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -12458,6 +12474,7 @@
 narrateur|Elle court, les mains ouvertes.
 narrateur|Elle tire l'anse d'un coup.
 narrateur|L'anse bute contre le pied.
+narrateur|Le seau recule, dans l'ombre.
 enfant-f|Il reste coincé.
 narrateur|Le sourire de Mila disparaît.
 narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
@@ -13065,17 +13082,17 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Près des chaînes, le ballon rouge attend. Il est lisse, un peu frais. Il roule sous la table ! Mila pousse trop fort. Le ballon rebondit une fois, mou. Il se cache derrière le pied. Le seau aussi ? Elle rampe, le vent dans le dos. Sa main trouve le cuir. Pas l'anse jaune. Ce n'est pas lui. On chasse le ballon ? Non. Mila refuse de foncer. Elle écoute le square. La chaîne se tait. Toc, sous le bois, minuscule. Le clou. Tu l'as entendu, toi.</t>
+          <t>Près des chaînes, le ballon rouge attend. Il est lisse, un peu frais. Il roule sous la table ! Mila pousse trop fort. Le ballon rebondit une fois, mou. Il se cache derrière le pied. Le seau aussi ? Elle rampe, le vent dans le dos. Sa main trouve le cuir. Pas l'anse jaune. Ce n'est pas lui. On chasse le ballon ? Non. Mila refuse de foncer. Elle écoute le square. La chaîne se tait. C'est l'heure, presque. Pas sans le toc. Toc, sous le bois, minuscule. Le clou. Tu l'as entendu, toi.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Près des chaînes, le ballon rouge attend. Il est lisse, un peu frais. Il roule sous la table ! Mila pousse trop fort. Le ballon rebondit une fois, mou. Il se cache derrière le pied. Le seau aussi ? Elle rampe, le vent dans le dos. Sa main trouve le cuir. Pas l'anse jaune. Ce n'est pas lui. On chasse le ballon ? Non. Mila refuse de foncer. Elle écoute le square. La chaîne se tait. Toc, sous le bois, minuscule. Le clou. Tu l'as entendu, toi.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Près des chaînes, le ballon rouge attend. Il est lisse, un peu frais. Il roule sous la table ! Mila pousse trop fort. Le ballon rebondit une fois, mou. Il se cache derrière le pied. Le seau aussi ? Elle rampe, le vent dans le dos. Sa main trouve le cuir. Pas l'anse jaune. Ce n'est pas lui. On chasse le ballon ? Non. Mila refuse de foncer. Elle écoute le square. La chaîne se tait. C'est l'heure, presque. Pas sans le toc. Toc, sous le bois, minuscule. Le clou. Tu l'as entendu, toi.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Près des chaînes, le ballon rouge attend. Il est lisse, un peu frais. Il roule sous la table ! Mila pousse trop fort. Le ballon rebondit une fois, mou. Il se cache derrière le pied. Le seau aussi ? Elle rampe, le vent dans le dos. Sa main trouve le cuir. Pas l'anse jaune. Ce n'est pas lui. On chasse le ballon ? Non. Mila refuse de foncer. Elle écoute le square. La chaîne se tait. Toc, sous le bois, minuscule. Le clou. Tu l'as entendu, toi.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Près des chaînes, le ballon rouge attend. Il est lisse, un peu frais. Il roule sous la table ! Mila pousse trop fort. Le ballon rebondit une fois, mou. Il se cache derrière le pied. Le seau aussi ? Elle rampe, le vent dans le dos. Sa main trouve le cuir. Pas l'anse jaune. Ce n'est pas lui. On chasse le ballon ? Non. Mila refuse de foncer. Elle écoute le square. La chaîne se tait. C'est l'heure, presque. Pas sans le toc. Toc, sous le bois, minuscule. Le clou. Tu l'as entendu, toi.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -13229,6 +13246,8 @@
 narrateur|Mila refuse de foncer.
 narrateur|Elle écoute le square.
 narrateur|La chaîne se tait.
+maman|C'est l'heure, presque.
+enfant-f|Pas sans le toc.
 narrateur|Toc, sous le bois, minuscule.
 enfant-f|Le clou.
 papa|Tu l'as entendu, toi.</t>
@@ -14596,17 +14615,17 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Mila revient vers la table. Le vent a touché le pain. Le seau, maman. Elle tire l'anse d'un coup. L'anse bute contre le pied. Il reste. Le manteau rouge bouge au dossier. Une manche tombe, large. Elle cache le clou de cuivre. On soulève tout ? Non. Mila refuse de foncer. Maman se met à sa hauteur. Personne ne dit le mot. Mila observe le seau, dans l'ombre. Elle écoute le bois. Le toc du clou. Tu l'as, ce son. La chaîne reste muette, derrière.</t>
+          <t>Mila revient vers la table. Le vent a touché le pain. Le seau, maman. Elle tire l'anse d'un coup. L'anse bute contre le pied. Il reste. Le manteau rouge bouge au dossier. Une manche tombe, large. Elle cache le clou de cuivre. On soulève tout ? Non. Mila refuse de foncer. Maman se met à sa hauteur. Personne ne dit le mot. Mila observe le seau, dans l'ombre. Elle écoute le bois. C'est l'heure, presque. Pas sans le toc. Le toc du clou. Tu l'as, ce son. La chaîne reste muette, derrière.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Mila revient vers la table. Le vent a touché le pain. Le seau, maman. Elle tire l'anse d'un coup. L'anse bute contre le pied. Il reste. Le manteau rouge bouge au dossier. Une manche tombe, large. Elle cache le clou de cuivre. On soulève tout ? Non. Mila refuse de foncer. Maman se met à sa hauteur. Personne ne dit le mot. Mila observe le seau, dans l'ombre. Elle écoute le bois. Le toc du clou. Tu l'as, ce son. La chaîne reste muette, derrière.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Mila revient vers la table. Le vent a touché le pain. Le seau, maman. Elle tire l'anse d'un coup. L'anse bute contre le pied. Il reste. Le manteau rouge bouge au dossier. Une manche tombe, large. Elle cache le clou de cuivre. On soulève tout ? Non. Mila refuse de foncer. Maman se met à sa hauteur. Personne ne dit le mot. Mila observe le seau, dans l'ombre. Elle écoute le bois. C'est l'heure, presque. Pas sans le toc. Le toc du clou. Tu l'as, ce son. La chaîne reste muette, derrière.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Mila revient vers la table. Le vent a touché le pain. Le seau, maman. Elle tire l'anse d'un coup. L'anse bute contre le pied. Il reste. Le manteau rouge bouge au dossier. Une manche tombe, large. Elle cache le clou de cuivre. On soulève tout ? Non. Mila refuse de foncer. Maman se met à sa hauteur. Personne ne dit le mot. Mila observe le seau, dans l'ombre. Elle écoute le bois. Le toc du clou. Tu l'as, ce son. La chaîne reste muette, derrière.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Mila revient vers la table. Le vent a touché le pain. Le seau, maman. Elle tire l'anse d'un coup. L'anse bute contre le pied. Il reste. Le manteau rouge bouge au dossier. Une manche tombe, large. Elle cache le clou de cuivre. On soulève tout ? Non. Mila refuse de foncer. Maman se met à sa hauteur. Personne ne dit le mot. Mila observe le seau, dans l'ombre. Elle écoute le bois. C'est l'heure, presque. Pas sans le toc. Le toc du clou. Tu l'as, ce son. La chaîne reste muette, derrière.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -14760,6 +14779,8 @@
 narrateur|Personne ne dit le mot.
 narrateur|Mila observe le seau, dans l'ombre.
 narrateur|Elle écoute le bois.
+papa|C'est l'heure, presque.
+enfant-f|Pas sans le toc.
 enfant-f|Le toc du clou.
 maman|Tu l'as, ce son.
 narrateur|La chaîne reste muette, derrière.</t>
@@ -16127,17 +16148,17 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Près des balançoires, le doudou gris attend. Le tissu a pris le vent. Il cherche le seau, avec moi. Mila le serre contre sa joue. L'oreille grise cache l'ombre. Elle cherche l'anse, trop vite. Sa main trouve le banc de pierre. Pas lui. Le sourire de Mila reste bas. L'oreille, un peu de côté ? Papa se met à sa hauteur. J'attends. Mila refuse de foncer. Elle écarte l'oreille, lentement. Un toc minuscule, sous le bois. Le clou. Tu l'as entendu, seule. L'oreille du doudou est froide.</t>
+          <t>Près des balançoires, le doudou gris attend. Le tissu a pris le vent. Il cherche le seau, avec moi. Mila le serre contre sa joue. L'oreille grise cache l'ombre. Elle cherche l'anse, trop vite. Sa main trouve le banc de pierre. Pas lui. Le sourire de Mila reste bas. L'oreille, un peu de côté ? Papa se met à sa hauteur. J'attends. Mila refuse de foncer. Elle écarte l'oreille, lentement. C'est l'heure, presque. Pas sans le toc. Un toc minuscule, sous le bois. Le clou. Tu l'as entendu, seule. L'oreille du doudou est froide.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Près des balançoires, le doudou gris attend. Le tissu a pris le vent. Il cherche le seau, avec moi. Mila le serre contre sa joue. L'oreille grise cache l'ombre. Elle cherche l'anse, trop vite. Sa main trouve le banc de pierre. Pas lui. Le sourire de Mila reste bas. L'oreille, un peu de côté ? Papa se met à sa hauteur. J'attends. Mila refuse de foncer. Elle écarte l'oreille, lentement. Un toc minuscule, sous le bois. Le clou. Tu l'as entendu, seule. L'oreille du doudou est froide.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Près des balançoires, le doudou gris attend. Le tissu a pris le vent. Il cherche le seau, avec moi. Mila le serre contre sa joue. L'oreille grise cache l'ombre. Elle cherche l'anse, trop vite. Sa main trouve le banc de pierre. Pas lui. Le sourire de Mila reste bas. L'oreille, un peu de côté ? Papa se met à sa hauteur. J'attends. Mila refuse de foncer. Elle écarte l'oreille, lentement. C'est l'heure, presque. Pas sans le toc. Un toc minuscule, sous le bois. Le clou. Tu l'as entendu, seule. L'oreille du doudou est froide.&lt;/prosody&gt;&lt;break time="540ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Près des balançoires, le doudou gris attend. Le tissu a pris le vent. Il cherche le seau, avec moi. Mila le serre contre sa joue. L'oreille grise cache l'ombre. Elle cherche l'anse, trop vite. Sa main trouve le banc de pierre. Pas lui. Le sourire de Mila reste bas. L'oreille, un peu de côté ? Papa se met à sa hauteur. J'attends. Mila refuse de foncer. Elle écarte l'oreille, lentement. Un toc minuscule, sous le bois. Le clou. Tu l'as entendu, seule. L'oreille du doudou est froide.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Près des balançoires, le doudou gris attend. Le tissu a pris le vent. Il cherche le seau, avec moi. Mila le serre contre sa joue. L'oreille grise cache l'ombre. Elle cherche l'anse, trop vite. Sa main trouve le banc de pierre. Pas lui. Le sourire de Mila reste bas. L'oreille, un peu de côté ? Papa se met à sa hauteur. J'attends. Mila refuse de foncer. Elle écarte l'oreille, lentement. C'est l'heure, presque. Pas sans le toc. Un toc minuscule, sous le bois. Le clou. Tu l'as entendu, seule. L'oreille du doudou est froide.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -16289,6 +16310,8 @@
 enfant-f|J'attends.
 narrateur|Mila refuse de foncer.
 narrateur|Elle écarte l'oreille, lentement.
+papa|C'est l'heure, presque.
+enfant-f|Pas sans le toc.
 narrateur|Un toc minuscule, sous le bois.
 enfant-f|Le clou.
 maman|Tu l'as entendu, seule.
@@ -17645,7 +17668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17758,6 +17781,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
